--- a/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/07_StructuredDefinition-Procedure-uv-ips_to_SDTM_PR.xlsx
+++ b/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/07_StructuredDefinition-Procedure-uv-ips_to_SDTM_PR.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28627"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/rbaker_cdisc_org/Documents/1 Real World Data - RWD/1_XSHARE/All Notes/Task 5.3/Meeting 5 - 2025-02-06/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05C86372-EA3B-4F8F-B3C4-25E4D3E8F709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{05C86372-EA3B-4F8F-B3C4-25E4D3E8F709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F827770-977D-4E1D-BFCB-7784B4949398}"/>
   <bookViews>
     <workbookView xWindow="-57030" yWindow="735" windowWidth="27000" windowHeight="14115" firstSheet="3" activeTab="3" xr2:uid="{15E96F3A-B263-4183-9117-FB31346D6DEA}"/>
-    <workbookView xWindow="-23148" yWindow="-1440" windowWidth="23256" windowHeight="13896" xr2:uid="{AC36A894-DF22-4E0A-ACE0-852F09361593}"/>
+    <workbookView xWindow="-23148" yWindow="-1440" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{AC36A894-DF22-4E0A-ACE0-852F09361593}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -2221,8 +2221,7 @@
     <t xml:space="preserve">CDISC SDTM Study Identifier/STUDYID </t>
   </si>
   <si>
-    <t xml:space="preserve">For each clinical research study, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.
-</t>
+    <t>In case there is no FHIR study ID (ResearchStudy or ResearchDefinition) available for the patient for which the immunization data is mapped, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.</t>
   </si>
   <si>
     <t xml:space="preserve">Study Identifier/STUDYID is a variable in CDISC Demographics domain that is a unique identifier for a study. STUDYID is used as a key in all CDISC SDTM datasets.
@@ -2557,7 +2556,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2673,6 +2672,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2785,7 +2791,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -2923,6 +2929,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -17846,14 +17855,14 @@
         <v>545</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60">
+    <row r="5" spans="1:4" ht="57.75">
       <c r="A5" s="21">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>546</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="54" t="s">
         <v>547</v>
       </c>
       <c r="D5" s="19" t="s">
@@ -18069,8 +18078,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="9455f3500918e16bfef273e9844733e2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2377a42c8d7fe4c42cf759ba29e74f14" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a46baf18-fe18-4a25-9dd7-6596c31699af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb735b3d8e016bb6466dda22f76823b1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47d37a05d05a9fe6c5dd27e72eaf287f" ns2:_="" ns3:_="">
     <xsd:import namespace="a46baf18-fe18-4a25-9dd7-6596c31699af"/>
     <xsd:import namespace="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b"/>
     <xsd:element name="properties">
@@ -18093,6 +18122,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -18123,7 +18153,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1eb19e05-fe62-4677-b8eb-b663d3127a74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1eb19e05-fe62-4677-b8eb-b663d3127a74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -18162,6 +18192,11 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -18177,7 +18212,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -18196,7 +18231,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -18213,8 +18248,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -18303,28 +18338,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a46baf18-fe18-4a25-9dd7-6596c31699af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D1A2DC-814B-4EB1-93B9-F2947EFEF204}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E3BB721-FB00-4DD6-814B-DE14AC45F25C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18332,5 +18347,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E3BB721-FB00-4DD6-814B-DE14AC45F25C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F88B2CC-62DF-4BEF-94EA-4DE374634402}"/>
 </file>